--- a/output/pdf_financials_xlsx/ILC.xlsx
+++ b/output/pdf_financials_xlsx/ILC.xlsx
@@ -5824,37 +5824,37 @@
         <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-1.31204</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-1.760878</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-1.396162</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.031063</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.005078</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.059644</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.577826</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>-1.268348</v>
+        <v>-5.159178</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-1.65443</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-0.595819</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-0.552995</v>
       </c>
     </row>
     <row r="119">
@@ -16814,7 +16814,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -24598,7 +24602,11 @@
           <t>Exploration and evaluation expenditure</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr">
         <is>
           <t>-</t>
@@ -26988,7 +26996,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ILC.xlsx
+++ b/output/pdf_financials_xlsx/ILC.xlsx
@@ -901,10 +901,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.003223</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000402</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -919,13 +919,13 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.006619</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.026928</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.027993</v>
       </c>
       <c r="M12" s="1" t="inlineStr">
         <is>
@@ -1628,10 +1628,10 @@
         <v>-1.03922</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.308884</v>
+        <v>-1.312107</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.233121</v>
+        <v>-1.233523</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-2.728841</v>
@@ -1646,13 +1646,13 @@
         <v>-4.478344</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.318229</v>
+        <v>-1.324848</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.351264</v>
+        <v>-2.378192</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.057741</v>
+        <v>-0.085734</v>
       </c>
       <c r="M27" s="1" t="inlineStr">
         <is>
@@ -1718,10 +1718,10 @@
         <v>-1.03922</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.308884</v>
+        <v>-1.312107</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.233121</v>
+        <v>-1.233523</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-2.728841</v>
@@ -1736,13 +1736,13 @@
         <v>-4.478344</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.316748</v>
+        <v>-1.323367</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.349116</v>
+        <v>-2.376044</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.056774</v>
+        <v>-0.084767</v>
       </c>
       <c r="M29" s="1" t="inlineStr">
         <is>
@@ -1948,37 +1948,37 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.001724</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.457912</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.745344</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.003855</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.162919</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.022543</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>10.961936</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>6.079566</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>2.672085</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.037931</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.139041</v>
       </c>
     </row>
     <row r="35">
@@ -2038,37 +2038,37 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.001724</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.457912</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.745344</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.023072</v>
+        <v>0.026927</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.08316999999999999</v>
+        <v>0.246089</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.022543</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>10.961936</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.374094</v>
+        <v>6.45366</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.177909</v>
+        <v>2.849994</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>-0.084776</v>
+        <v>-0.046845</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.139041</v>
       </c>
     </row>
     <row r="37">
@@ -2578,37 +2578,37 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.001724</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.48885</v>
+        <v>0.030938</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.757018</v>
+        <v>0.011674</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.034288</v>
+        <v>0.030433</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.2065</v>
+        <v>0.043581</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.045198</v>
+        <v>0.022655</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>11.089224</v>
+        <v>0.127288</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>6.566299</v>
+        <v>0.486733</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>2.717218</v>
+        <v>0.045133</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>2.732963</v>
+        <v>2.695032</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.188899</v>
+        <v>0.049858</v>
       </c>
     </row>
     <row r="49">
@@ -6101,7 +6101,7 @@
         <v>0</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-0.063275</v>
       </c>
       <c r="I124" s="3" t="n">
         <v>0</v>
@@ -6144,7 +6144,7 @@
         <v>0</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-0.063275</v>
       </c>
       <c r="I125" s="3" t="n">
         <v>0</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -14908,7 +14908,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -25356,7 +25356,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -34564,7 +34568,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -36144,7 +36148,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -37416,7 +37420,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -40908,7 +40912,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
@@ -42530,7 +42534,7 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
